--- a/resources/M626/spc_cpk_decoration.xlsx
+++ b/resources/M626/spc_cpk_decoration.xlsx
@@ -2600,10 +2600,10 @@
         <v>46190.79921296296</v>
       </c>
       <c r="J49">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
       <c r="K49">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>46190.79921296296</v>
       </c>
       <c r="J51">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
       <c r="K51">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         <v>46174.95023148148</v>
       </c>
       <c r="J53">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
       <c r="K53">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>46174.95023148148</v>
       </c>
       <c r="J55">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
       <c r="K55">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -4614,10 +4614,10 @@
         <v>46183.9808912037</v>
       </c>
       <c r="J102">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
       <c r="K102">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4728,10 +4728,10 @@
         <v>46183.9808912037</v>
       </c>
       <c r="J105">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
       <c r="K105">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>46192.85702546296</v>
       </c>
       <c r="J110">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
       <c r="K110">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -5032,10 +5032,10 @@
         <v>46192.85702546296</v>
       </c>
       <c r="J113">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
       <c r="K113">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -5982,10 +5982,10 @@
         <v>46193.32494212963</v>
       </c>
       <c r="J138">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
       <c r="K138">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>46193.32494212963</v>
       </c>
       <c r="J140">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
       <c r="K140">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>46187.56212962963</v>
       </c>
       <c r="J200">
-        <v>3.124467950828476</v>
+        <v>3.124467950828475</v>
       </c>
       <c r="K200">
-        <v>3.124467950828476</v>
+        <v>3.124467950828475</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8718,10 +8718,10 @@
         <v>46174.81490740741</v>
       </c>
       <c r="J210">
-        <v>1.404885478325891</v>
+        <v>1.40488547832589</v>
       </c>
       <c r="K210">
-        <v>1.404885478325891</v>
+        <v>1.40488547832589</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>46176.85328703704</v>
       </c>
       <c r="J212">
-        <v>2.491685225867085</v>
+        <v>2.491685225867086</v>
       </c>
       <c r="K212">
-        <v>2.491685225867085</v>
+        <v>2.491685225867086</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -9706,10 +9706,10 @@
         <v>46181.9305787037</v>
       </c>
       <c r="J236">
-        <v>3.210399360801442</v>
+        <v>3.210399360801443</v>
       </c>
       <c r="K236">
-        <v>3.210399360801442</v>
+        <v>3.210399360801443</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9782,10 +9782,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J238">
-        <v>3.473296225913956</v>
+        <v>3.473296225913955</v>
       </c>
       <c r="K238">
-        <v>3.473296225913956</v>
+        <v>3.473296225913955</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -10086,10 +10086,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J246">
-        <v>1.978853450574098</v>
+        <v>1.978853450574099</v>
       </c>
       <c r="K246">
-        <v>1.978853450574098</v>
+        <v>1.978853450574099</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -11036,10 +11036,10 @@
         <v>46175.98122685185</v>
       </c>
       <c r="J271">
-        <v>4.758989576321312</v>
+        <v>4.758989576321313</v>
       </c>
       <c r="K271">
-        <v>4.758989576321312</v>
+        <v>4.758989576321313</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -11302,10 +11302,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J278">
-        <v>4.448379640390239</v>
+        <v>4.44837964039024</v>
       </c>
       <c r="K278">
-        <v>4.448379640390239</v>
+        <v>4.44837964039024</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11492,10 +11492,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J283">
-        <v>4.135629187404322</v>
+        <v>4.135629187404321</v>
       </c>
       <c r="K283">
-        <v>4.135629187404322</v>
+        <v>4.135629187404321</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11682,10 +11682,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J288">
-        <v>2.13289939599393</v>
+        <v>2.132899395993929</v>
       </c>
       <c r="K288">
-        <v>2.13289939599393</v>
+        <v>2.132899395993929</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -12594,10 +12594,10 @@
         <v>46176.85328703704</v>
       </c>
       <c r="J312">
-        <v>4.803816545084888</v>
+        <v>4.803816545084887</v>
       </c>
       <c r="K312">
-        <v>4.803816545084888</v>
+        <v>4.803816545084887</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12632,10 +12632,10 @@
         <v>46177.79724537037</v>
       </c>
       <c r="J313">
-        <v>4.467542831680012</v>
+        <v>4.46754283168001</v>
       </c>
       <c r="K313">
-        <v>4.467542831680012</v>
+        <v>4.46754283168001</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12670,10 +12670,10 @@
         <v>46179.84344907408</v>
       </c>
       <c r="J314">
-        <v>3.964382272784407</v>
+        <v>3.964382272784406</v>
       </c>
       <c r="K314">
-        <v>3.964382272784407</v>
+        <v>3.964382272784406</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12822,10 +12822,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J318">
-        <v>4.871659350617075</v>
+        <v>4.871659350617077</v>
       </c>
       <c r="K318">
-        <v>4.871659350617075</v>
+        <v>4.871659350617077</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12936,10 +12936,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J321">
-        <v>5.26681464999815</v>
+        <v>5.266814649998149</v>
       </c>
       <c r="K321">
-        <v>5.26681464999815</v>
+        <v>5.266814649998149</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -13012,10 +13012,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J323">
-        <v>4.173442424252206</v>
+        <v>4.173442424252205</v>
       </c>
       <c r="K323">
-        <v>4.173442424252206</v>
+        <v>4.173442424252205</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -13278,10 +13278,10 @@
         <v>46174.94690972222</v>
       </c>
       <c r="J330">
-        <v>7.589856339205542</v>
+        <v>7.589856339205541</v>
       </c>
       <c r="K330">
-        <v>7.589856339205542</v>
+        <v>7.589856339205541</v>
       </c>
       <c r="L330" t="b">
         <v>0</v>
@@ -13582,10 +13582,10 @@
         <v>46182.96581018518</v>
       </c>
       <c r="J338">
-        <v>7.297598095080794</v>
+        <v>7.297598095080793</v>
       </c>
       <c r="K338">
-        <v>7.297598095080794</v>
+        <v>7.297598095080793</v>
       </c>
       <c r="L338" t="b">
         <v>0</v>
@@ -13772,10 +13772,10 @@
         <v>46205.74840277778</v>
       </c>
       <c r="J343">
-        <v>5.002728289455207</v>
+        <v>5.002728289455206</v>
       </c>
       <c r="K343">
-        <v>5.002728289455207</v>
+        <v>5.002728289455206</v>
       </c>
       <c r="L343" t="b">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>46206.6680324074</v>
       </c>
       <c r="J344">
-        <v>6.868403886344061</v>
+        <v>6.868403886344059</v>
       </c>
       <c r="K344">
-        <v>6.868403886344061</v>
+        <v>6.868403886344059</v>
       </c>
       <c r="L344" t="b">
         <v>0</v>
@@ -14380,10 +14380,10 @@
         <v>46182.96581018518</v>
       </c>
       <c r="J359">
-        <v>1.89253499115685</v>
+        <v>1.892534991156849</v>
       </c>
       <c r="K359">
-        <v>1.89253499115685</v>
+        <v>1.892534991156849</v>
       </c>
       <c r="L359" t="b">
         <v>0</v>
@@ -15026,10 +15026,10 @@
         <v>46178.9991087963</v>
       </c>
       <c r="J376">
-        <v>9.17126760773591</v>
+        <v>9.171267607735908</v>
       </c>
       <c r="K376">
-        <v>9.17126760773591</v>
+        <v>9.171267607735908</v>
       </c>
       <c r="L376" t="b">
         <v>0</v>
@@ -16090,10 +16090,10 @@
         <v>46203.9103125</v>
       </c>
       <c r="J404">
-        <v>3.291970900992209</v>
+        <v>3.29197090099221</v>
       </c>
       <c r="K404">
-        <v>3.291970900992209</v>
+        <v>3.29197090099221</v>
       </c>
       <c r="L404" t="b">
         <v>0</v>
@@ -16204,10 +16204,10 @@
         <v>46206.66802083333</v>
       </c>
       <c r="J407">
-        <v>3.078750218465228</v>
+        <v>3.078750218465227</v>
       </c>
       <c r="K407">
-        <v>3.078750218465228</v>
+        <v>3.078750218465227</v>
       </c>
       <c r="L407" t="b">
         <v>0</v>
@@ -17268,10 +17268,10 @@
         <v>46175.97753472222</v>
       </c>
       <c r="J435">
-        <v>1.592917901067202</v>
+        <v>1.592917901067203</v>
       </c>
       <c r="K435">
-        <v>1.592917901067202</v>
+        <v>1.592917901067203</v>
       </c>
       <c r="L435" t="b">
         <v>0</v>
@@ -17686,10 +17686,10 @@
         <v>46184.68292824074</v>
       </c>
       <c r="J446">
-        <v>1.455965109029581</v>
+        <v>1.45596510902958</v>
       </c>
       <c r="K446">
-        <v>1.455965109029581</v>
+        <v>1.45596510902958</v>
       </c>
       <c r="L446" t="b">
         <v>0</v>
@@ -18370,10 +18370,10 @@
         <v>46182.60833333333</v>
       </c>
       <c r="J464">
-        <v>1.435540527273854</v>
+        <v>1.435540527273855</v>
       </c>
       <c r="K464">
-        <v>1.435540527273854</v>
+        <v>1.435540527273855</v>
       </c>
       <c r="L464" t="b">
         <v>0</v>
@@ -18522,10 +18522,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J468">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K468">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="L468" t="b">
         <v>0</v>
@@ -18636,10 +18636,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J471">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K471">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="L471" t="b">
         <v>0</v>
@@ -18750,10 +18750,10 @@
         <v>46182.60833333333</v>
       </c>
       <c r="J474">
-        <v>2.502953491729751</v>
+        <v>2.502953491729752</v>
       </c>
       <c r="K474">
-        <v>2.502953491729751</v>
+        <v>2.502953491729752</v>
       </c>
       <c r="L474" t="b">
         <v>0</v>
@@ -18826,10 +18826,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J476">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K476">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="L476" t="b">
         <v>0</v>
@@ -19320,10 +19320,10 @@
         <v>46180.393125</v>
       </c>
       <c r="J489">
-        <v>2.837561306383012</v>
+        <v>2.837561306383013</v>
       </c>
       <c r="K489">
-        <v>2.837561306383012</v>
+        <v>2.837561306383013</v>
       </c>
       <c r="L489" t="b">
         <v>0</v>
@@ -19358,10 +19358,10 @@
         <v>46186.12424768518</v>
       </c>
       <c r="J490">
-        <v>2.874004779757791</v>
+        <v>2.87400477975779</v>
       </c>
       <c r="K490">
-        <v>2.874004779757791</v>
+        <v>2.87400477975779</v>
       </c>
       <c r="L490" t="b">
         <v>0</v>
@@ -19586,10 +19586,10 @@
         <v>46183.154375</v>
       </c>
       <c r="J496">
-        <v>2.645265851074052</v>
+        <v>2.645265851074053</v>
       </c>
       <c r="K496">
-        <v>2.645265851074052</v>
+        <v>2.645265851074053</v>
       </c>
       <c r="L496" t="b">
         <v>0</v>
@@ -19776,10 +19776,10 @@
         <v>46180.0500462963</v>
       </c>
       <c r="J501">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
       <c r="K501">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
       <c r="L501" t="b">
         <v>0</v>
@@ -19890,10 +19890,10 @@
         <v>46180.0500462963</v>
       </c>
       <c r="J504">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
       <c r="K504">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
       <c r="L504" t="b">
         <v>0</v>
@@ -20080,10 +20080,10 @@
         <v>46210.61064814815</v>
       </c>
       <c r="J509">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K509">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="L509" t="b">
         <v>0</v>
@@ -20194,10 +20194,10 @@
         <v>46210.61064814815</v>
       </c>
       <c r="J512">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K512">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="L512" t="b">
         <v>0</v>
@@ -20346,10 +20346,10 @@
         <v>46210.61064814815</v>
       </c>
       <c r="J516">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K516">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="L516" t="b">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>46180.01618055555</v>
       </c>
       <c r="J538">
-        <v>1.61466438302404</v>
+        <v>1.614664383024041</v>
       </c>
       <c r="K538">
-        <v>1.61466438302404</v>
+        <v>1.614664383024041</v>
       </c>
       <c r="L538" t="b">
         <v>0</v>
@@ -22246,10 +22246,10 @@
         <v>46214.6469212963</v>
       </c>
       <c r="J566">
-        <v>6.264830902260329</v>
+        <v>6.26483090226033</v>
       </c>
       <c r="K566">
-        <v>6.264830902260329</v>
+        <v>6.26483090226033</v>
       </c>
       <c r="L566" t="b">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>46177.85769675926</v>
       </c>
       <c r="J569">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
       <c r="K569">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
       <c r="L569" t="b">
         <v>0</v>
@@ -22474,10 +22474,10 @@
         <v>46177.85769675926</v>
       </c>
       <c r="J572">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
       <c r="K572">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
       <c r="L572" t="b">
         <v>0</v>
